--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_377_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_377_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>29</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
         <v>5</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -2511,16 +2511,16 @@
         <v>22</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2707,7 +2707,7 @@
         <v>30</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3043,16 +3043,16 @@
         <v>141</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X26" t="n">
         <v>28</v>
@@ -3704,7 +3704,7 @@
         <v>30</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -4096,16 +4096,16 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
         <v>4</v>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -5076,16 +5076,16 @@
         <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>4</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6000,16 +6000,16 @@
         <v>101</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X44" t="n">
         <v>14</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_377_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_377_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>13</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
         <v>15</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,10 +1543,10 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2523,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3055,14 +3055,14 @@
         <v>9</v>
       </c>
       <c r="X26" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -4108,14 +4108,14 @@
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA34" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -5088,14 +5088,14 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -6012,14 +6012,14 @@
         <v>4</v>
       </c>
       <c r="X44" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
